--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -266,7 +266,7 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">string
+    <t xml:space="preserve">id
 </t>
   </si>
   <si>
@@ -338,7 +338,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4B/extensibility.html) for a list).</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -266,7 +266,7 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">id
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
@@ -338,7 +338,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4B/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}

--- a/branches/Richard/StructureDefinition-patient-age-months.xlsx
+++ b/branches/Richard/StructureDefinition-patient-age-months.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
